--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.01075751010842</v>
+        <v>5.364248095392618</v>
       </c>
       <c r="D2" t="n">
-        <v>31.53507356146108</v>
+        <v>5.124449453737426</v>
       </c>
       <c r="E2" t="n">
-        <v>14.401465539944</v>
+        <v>2.3402381502409</v>
       </c>
       <c r="F2" t="n">
-        <v>14.75895040938607</v>
+        <v>2.398329441525236</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.44740944696271</v>
+        <v>2.510204035131441</v>
       </c>
       <c r="D3" t="n">
-        <v>15.89026640055408</v>
+        <v>2.582168290090039</v>
       </c>
       <c r="E3" t="n">
-        <v>14.401465539944</v>
+        <v>2.3402381502409</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75895040938607</v>
+        <v>2.398329441525236</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.93579344392513</v>
+        <v>4.702066434637834</v>
       </c>
       <c r="D4" t="n">
-        <v>27.74445267723447</v>
+        <v>4.508473560050602</v>
       </c>
       <c r="E4" t="n">
-        <v>14.401465539944</v>
+        <v>2.3402381502409</v>
       </c>
       <c r="F4" t="n">
-        <v>14.75895040938607</v>
+        <v>2.398329441525236</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.167760668684803</v>
+        <v>1.164761108661281</v>
       </c>
       <c r="D5" t="n">
-        <v>5.609318477156819</v>
+        <v>0.9115142525379831</v>
       </c>
       <c r="E5" t="n">
-        <v>14.401465539944</v>
+        <v>2.3402381502409</v>
       </c>
       <c r="F5" t="n">
-        <v>14.75895040938607</v>
+        <v>2.398329441525236</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.36077873543331</v>
+        <v>7.696126544507914</v>
       </c>
       <c r="D6" t="n">
-        <v>46.29236750825803</v>
+        <v>7.52250972009193</v>
       </c>
       <c r="E6" t="n">
-        <v>14.401465539944</v>
+        <v>2.3402381502409</v>
       </c>
       <c r="F6" t="n">
-        <v>14.75895040938607</v>
+        <v>2.398329441525236</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.2200682945155</v>
+        <v>7.185761097858768</v>
       </c>
       <c r="D7" t="n">
-        <v>45.76800823034799</v>
+        <v>7.437301337431549</v>
       </c>
       <c r="E7" t="n">
-        <v>14.401465539944</v>
+        <v>2.3402381502409</v>
       </c>
       <c r="F7" t="n">
-        <v>14.75895040938607</v>
+        <v>2.398329441525236</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
